--- a/marketing_forms/008_global_market_insights_survey_form--marketing_forms.xlsx
+++ b/marketing_forms/008_global_market_insights_survey_form--marketing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_18-24'}</t>
+          <t>age_group_18-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 18-24'}</t>
+          <t>Age Group 18-24</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_25-34'}</t>
+          <t>age_group_25-34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 25-34'}</t>
+          <t>Age Group 25-34</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_35-44'}</t>
+          <t>age_group_35-44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 35-44'}</t>
+          <t>Age Group 35-44</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_45-54'}</t>
+          <t>age_group_45-54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 45-54'}</t>
+          <t>Age Group 45-54</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_55-64'}</t>
+          <t>age_group_55-64</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 55-64'}</t>
+          <t>Age Group 55-64</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'age_group_65_or_above'}</t>
+          <t>age_group_65_or_above</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Age Group 65 or above'}</t>
+          <t>Age Group 65 or above</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_$25,000'}</t>
+          <t>less_than_$25,000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Less than $25,000'}</t>
+          <t>Less than $25,000</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'$25,000-$49,999'}</t>
+          <t>$25,000-$49,999</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '$25,000-$49,999'}</t>
+          <t>$25,000-$49,999</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'$50,000-$74,999'}</t>
+          <t>$50,000-$74,999</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '$50,000-$74,999'}</t>
+          <t>$50,000-$74,999</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'$75,000-$99,999'}</t>
+          <t>$75,000-$99,999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': '$75,000-$99,999'}</t>
+          <t>$75,000-$99,999</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'$100,000_or_more'}</t>
+          <t>$100,000_or_more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': '$100,000 or more'}</t>
+          <t>$100,000 or more</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'less_than_high_school'}</t>
+          <t>less_than_high_school</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Less than High School'}</t>
+          <t>Less than High School</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Some college'}</t>
+          <t>Some college</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'College'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'postgraduate'}</t>
+          <t>postgraduate</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Postgraduate'}</t>
+          <t>Postgraduate</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'divorced'}</t>
+          <t>divorced</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Divorced'}</t>
+          <t>Divorced</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'widowed'}</t>
+          <t>widowed</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Widowed'}</t>
+          <t>Widowed</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'in_a_domestic_partnership'}</t>
+          <t>in_a_domestic_partnership</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'In a domestic partnership'}</t>
+          <t>In a domestic partnership</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'5_or_more'}</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': '5 or more'}</t>
+          <t>5 or more</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'5_or_more'}</t>
+          <t>5_or_more</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': '5 or more'}</t>
+          <t>5 or more</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'japanese'}</t>
+          <t>japanese</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Japanese'}</t>
+          <t>Japanese</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'arabic'}</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Arabic'}</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'hindi'}</t>
+          <t>hindi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Hindi'}</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
